--- a/Tagihan/2026/September/SDN Mabuun.xlsx
+++ b/Tagihan/2026/September/SDN Mabuun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\September\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{930E97C8-6BDF-4A1A-B284-DF329726BF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6E06CD-63D2-4AFF-8664-A798BE7838A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12525" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>NO.</t>
   </si>
@@ -100,12 +100,6 @@
       </rPr>
       <t xml:space="preserve"> September 2026</t>
     </r>
-  </si>
-  <si>
-    <t>Konektor LAN</t>
-  </si>
-  <si>
-    <t>Pcs</t>
   </si>
 </sst>
 </file>
@@ -346,17 +340,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -365,7 +361,24 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -376,11 +389,26 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -389,31 +417,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -531,16 +537,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -621,13 +627,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -962,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H38"/>
+  <dimension ref="B5:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1044,7 +1050,7 @@
       <c r="G14" s="40"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="42" t="s">
         <v>0</v>
       </c>
@@ -1064,58 +1070,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
+    <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="23">
         <v>1</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="16">
-        <v>6000</v>
-      </c>
-      <c r="G17" s="16">
-        <f t="shared" ref="G17:G18" si="0">F17*D17</f>
-        <v>24000</v>
+      <c r="C17" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="23">
+        <v>1</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="15">
+        <v>100000</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" ref="G17" si="0">F17*D17</f>
+        <v>100000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23">
-        <v>2</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="23">
-        <v>1</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="15">
-        <v>100000</v>
-      </c>
-      <c r="G18" s="15">
-        <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="22"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="14"/>
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="23"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="17"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1123,7 +1116,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="17"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1131,7 +1124,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="23"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="17"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1139,7 +1132,7 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="17"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1147,18 +1140,18 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="17"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="C25" s="17"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="14"/>
       <c r="G25" s="16"/>
     </row>
@@ -1174,92 +1167,84 @@
       <c r="B27" s="2"/>
       <c r="C27" s="17"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="16"/>
-    </row>
-    <row r="28" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="34" t="s">
+      <c r="E27" s="19"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="18">
-        <f>SUM(G17:G28)</f>
-        <v>124000</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="32" spans="2:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B32" s="37" t="s">
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="18">
+        <f>SUM(G17:G27)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="31" spans="2:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B31" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="38" t="s">
+      <c r="C31" s="37"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="38"/>
-    </row>
-    <row r="36" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
+      <c r="G31" s="38"/>
+    </row>
+    <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="12"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="13"/>
+      <c r="B37" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="12"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B37:G37"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F31:G31"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
